--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-07.xlsx
@@ -769,22 +769,22 @@
         <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N2" t="n">
         <v>3.85</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.97</v>
-      </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
         <v>1.97</v>
@@ -793,134 +793,134 @@
         <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
         <v>1.55</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AB2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
         <v>16</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AS2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
       </c>
       <c r="AW2" t="n">
         <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.4</v>
+        <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.58</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.56</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.58</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.7</v>
+        <v>19</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         <v>3.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
         <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="T3" t="n">
         <v>1.39</v>
@@ -1017,10 +1017,10 @@
         <v>55</v>
       </c>
       <c r="AB3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AD3" t="n">
         <v>18.5</v>
@@ -1032,7 +1032,7 @@
         <v>25</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH3" t="n">
         <v>14.5</v>
@@ -1041,7 +1041,7 @@
         <v>32</v>
       </c>
       <c r="AJ3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AK3" t="n">
         <v>24</v>
@@ -1059,16 +1059,16 @@
         <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>22</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>19.5</v>
@@ -1095,7 +1095,7 @@
         <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
         <v>16.5</v>
@@ -1104,7 +1104,7 @@
         <v>19</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF3" t="n">
         <v>6.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
         <v>1.83</v>
@@ -1178,7 +1178,7 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
         <v>1.7</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G6" t="n">
         <v>2.56</v>
@@ -1542,7 +1542,7 @@
         <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
         <v>3.85</v>
@@ -1551,7 +1551,7 @@
         <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1560,10 +1560,10 @@
         <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q6" t="n">
         <v>1.6</v>
@@ -1572,16 +1572,16 @@
         <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
         <v>1.64</v>
@@ -1590,7 +1590,7 @@
         <v>29</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z6" t="n">
         <v>27</v>
@@ -1611,7 +1611,7 @@
         <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG6" t="n">
         <v>15</v>
@@ -1650,7 +1650,7 @@
         <v>18.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -1674,10 +1674,10 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB6" t="n">
         <v>5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
         <v>20</v>
@@ -1686,7 +1686,7 @@
         <v>23</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="G9" t="n">
         <v>2.12</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="G10" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>2.74</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G11" t="n">
         <v>3.45</v>
       </c>
       <c r="H11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I11" t="n">
         <v>2.96</v>
@@ -2518,7 +2518,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
         <v>5.2</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>2.82</v>
       </c>
       <c r="O12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
         <v>3.9</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.6</v>
       </c>
       <c r="H15" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="I15" t="n">
         <v>3.05</v>
@@ -3294,7 +3294,7 @@
         <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="H16" t="n">
         <v>3.7</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G17" t="n">
         <v>1.95</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>3.9</v>
       </c>
       <c r="G18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="I18" t="n">
         <v>1.88</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
         <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
@@ -4282,7 +4282,7 @@
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>1.07</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H21" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I21" t="n">
         <v>60</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G22" t="n">
         <v>1.82</v>
@@ -4649,7 +4649,7 @@
         <v>5.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4697,7 +4697,7 @@
         <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA22" t="n">
         <v>180</v>
@@ -4724,7 +4724,7 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
         <v>19</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -4840,10 +4840,10 @@
         <v>2.36</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
         <v>1.62</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I24" t="n">
         <v>2.16</v>
@@ -5040,7 +5040,7 @@
         <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q24" t="n">
         <v>1.68</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5228,13 +5228,13 @@
         <v>3.65</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J25" t="n">
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>6.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
         <v>4.8</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>3.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
         <v>3.3</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G28" t="n">
         <v>5.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="I28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G29" t="n">
         <v>1.97</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>4.2</v>
       </c>
       <c r="G30" t="n">
-        <v>410</v>
+        <v>13</v>
       </c>
       <c r="H30" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="I30" t="n">
         <v>2.06</v>
@@ -6204,7 +6204,7 @@
         <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>2.08</v>
       </c>
       <c r="G31" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H31" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I31" t="n">
         <v>3.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
         <v>4.3</v>
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q31" t="n">
         <v>1.65</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>2.42</v>
       </c>
       <c r="G42" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="H42" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
@@ -8547,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q42" t="n">
         <v>1.94</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G43" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H43" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="K43" t="n">
-        <v>630</v>
+        <v>4.7</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8735,16 +8735,16 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="O43" t="n">
         <v>1.36</v>
       </c>
       <c r="P43" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.36</v>
+        <v>1.76</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>1.71</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9908,7 @@
         <v>2.46</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R49" t="n">
         <v>1.6</v>
@@ -10019,7 +10019,7 @@
         <v>24</v>
       </c>
       <c r="BB49" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BC49" t="n">
         <v>29</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10069,16 +10069,16 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G50" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H50" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I50" t="n">
         <v>2.5</v>
-      </c>
-      <c r="I50" t="n">
-        <v>2.56</v>
       </c>
       <c r="J50" t="n">
         <v>3.55</v>
@@ -10159,10 +10159,10 @@
         <v>40</v>
       </c>
       <c r="AJ50" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK50" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL50" t="n">
         <v>46</v>
@@ -10171,7 +10171,7 @@
         <v>110</v>
       </c>
       <c r="AN50" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO50" t="n">
         <v>22</v>
@@ -10180,13 +10180,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR50" t="n">
         <v>14.5</v>
       </c>
       <c r="AS50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AT50" t="n">
         <v>11</v>
@@ -10207,13 +10207,13 @@
         <v>12</v>
       </c>
       <c r="AZ50" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA50" t="n">
         <v>32</v>
       </c>
       <c r="BB50" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC50" t="n">
         <v>28</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
         <v>1.49</v>
       </c>
       <c r="S51" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T51" t="n">
         <v>1.63</v>
@@ -10317,7 +10317,7 @@
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y51" t="n">
         <v>15.5</v>
@@ -10329,7 +10329,7 @@
         <v>60</v>
       </c>
       <c r="AB51" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC51" t="n">
         <v>8.6</v>
@@ -10362,7 +10362,7 @@
         <v>34</v>
       </c>
       <c r="AM51" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AN51" t="n">
         <v>16</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10481,25 +10481,25 @@
         <v>1.03</v>
       </c>
       <c r="N52" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O52" t="n">
         <v>1.16</v>
       </c>
       <c r="P52" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R52" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S52" t="n">
         <v>2.2</v>
       </c>
       <c r="T52" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U52" t="n">
         <v>2.36</v>
@@ -10535,13 +10535,13 @@
         <v>90</v>
       </c>
       <c r="AF52" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG52" t="n">
         <v>10.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI52" t="n">
         <v>75</v>
@@ -10565,13 +10565,13 @@
         <v>75</v>
       </c>
       <c r="AP52" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ52" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR52" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AS52" t="n">
         <v>48</v>
@@ -10583,7 +10583,7 @@
         <v>11.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW52" t="n">
         <v>36</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -10660,10 +10660,10 @@
         <v>1.65</v>
       </c>
       <c r="I53" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J53" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K53" t="n">
         <v>4.7</v>
@@ -10690,7 +10690,7 @@
         <v>1.71</v>
       </c>
       <c r="S53" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T53" t="n">
         <v>1.62</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.04</v>
+        <v>1.4</v>
       </c>
       <c r="G55" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="H55" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I55" t="n">
         <v>3.5</v>
       </c>
       <c r="J55" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="K55" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11427,10 +11427,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G57" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H57" t="n">
         <v>3.15</v>
@@ -11439,10 +11439,10 @@
         <v>4.9</v>
       </c>
       <c r="J57" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K57" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -11818,19 +11818,19 @@
         <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H59" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I59" t="n">
         <v>2.12</v>
       </c>
       <c r="J59" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K59" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
         <v>3.3</v>
       </c>
       <c r="I60" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -12042,7 +12042,7 @@
         <v>1.64</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12397,22 +12397,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="G62" t="n">
         <v>4.2</v>
       </c>
       <c r="H62" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="I62" t="n">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="J62" t="n">
         <v>2.84</v>
       </c>
       <c r="K62" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12427,10 +12427,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
         <v>2.9</v>
       </c>
       <c r="G64" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H64" t="n">
         <v>2.42</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G65" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H65" t="n">
         <v>2.38</v>
@@ -12991,7 +12991,7 @@
         <v>2.72</v>
       </c>
       <c r="J65" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K65" t="n">
         <v>4.4</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q65" t="n">
         <v>1.86</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13173,16 +13173,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G66" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H66" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I66" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J66" t="n">
         <v>3.7</v>
@@ -13206,7 +13206,7 @@
         <v>1.84</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G67" t="n">
         <v>2.58</v>
@@ -13376,7 +13376,7 @@
         <v>3.15</v>
       </c>
       <c r="I67" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="J67" t="n">
         <v>3.15</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13564,16 +13564,16 @@
         <v>1.31</v>
       </c>
       <c r="G68" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="H68" t="n">
         <v>6</v>
       </c>
       <c r="I68" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J68" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="K68" t="n">
         <v>7.2</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -13776,19 +13776,19 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O69" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P69" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R69" t="n">
         <v>1.22</v>
@@ -13800,7 +13800,7 @@
         <v>2.04</v>
       </c>
       <c r="U69" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -13809,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y69" t="n">
         <v>11</v>
@@ -13854,16 +13854,16 @@
         <v>65</v>
       </c>
       <c r="AM69" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN69" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO69" t="n">
         <v>90</v>
       </c>
       <c r="AP69" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ69" t="n">
         <v>9.6</v>
@@ -13884,7 +13884,7 @@
         <v>14</v>
       </c>
       <c r="AW69" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX69" t="n">
         <v>11</v>
@@ -13896,29 +13896,29 @@
         <v>19</v>
       </c>
       <c r="BA69" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB69" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BC69" t="n">
         <v>22</v>
       </c>
       <c r="BD69" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG69" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BE69" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF69" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG69" t="n">
-        <v>10</v>
-      </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
         <v>2.06</v>
       </c>
       <c r="G72" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H72" t="n">
         <v>3.95</v>
@@ -14349,7 +14349,7 @@
         <v>5.1</v>
       </c>
       <c r="J72" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K72" t="n">
         <v>3.85</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15307,13 +15307,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G77" t="n">
         <v>1.84</v>
       </c>
       <c r="H77" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I77" t="n">
         <v>5.1</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H78" t="n">
         <v>3.15</v>
@@ -15516,7 +15516,7 @@
         <v>3.2</v>
       </c>
       <c r="K78" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -15695,22 +15695,22 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G79" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H79" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I79" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J79" t="n">
         <v>5.7</v>
       </c>
       <c r="K79" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -15725,10 +15725,10 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G81" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I81" t="n">
         <v>1.74</v>
@@ -16098,7 +16098,7 @@
         <v>3.7</v>
       </c>
       <c r="K81" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="Q81" t="n">
         <v>1.66</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16280,13 +16280,13 @@
         <v>1.65</v>
       </c>
       <c r="G82" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H82" t="n">
         <v>6.2</v>
       </c>
       <c r="I82" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J82" t="n">
         <v>4</v>
@@ -16322,7 +16322,7 @@
         <v>1.96</v>
       </c>
       <c r="U82" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V82" t="n">
         <v>0</v>
@@ -16367,10 +16367,10 @@
         <v>95</v>
       </c>
       <c r="AJ82" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK82" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL82" t="n">
         <v>40</v>
@@ -16379,7 +16379,7 @@
         <v>150</v>
       </c>
       <c r="AN82" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO82" t="n">
         <v>140</v>
@@ -16394,7 +16394,7 @@
         <v>42</v>
       </c>
       <c r="AS82" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT82" t="n">
         <v>7.4</v>
@@ -16418,7 +16418,7 @@
         <v>18.5</v>
       </c>
       <c r="BA82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB82" t="n">
         <v>13.5</v>
@@ -16430,17 +16430,17 @@
         <v>30</v>
       </c>
       <c r="BE82" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF82" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG82" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -16859,16 +16859,16 @@
         </is>
       </c>
       <c r="F85" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G85" t="n">
         <v>1.65</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1.66</v>
       </c>
       <c r="H85" t="n">
         <v>6</v>
       </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J85" t="n">
         <v>4.3</v>
@@ -16889,7 +16889,7 @@
         <v>1.29</v>
       </c>
       <c r="P85" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q85" t="n">
         <v>1.84</v>
@@ -16916,10 +16916,10 @@
         <v>17.5</v>
       </c>
       <c r="Y85" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z85" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA85" t="n">
         <v>170</v>
@@ -16928,13 +16928,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC85" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE85" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF85" t="n">
         <v>10</v>
@@ -16946,13 +16946,13 @@
         <v>22</v>
       </c>
       <c r="AI85" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ85" t="n">
         <v>16.5</v>
       </c>
       <c r="AK85" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL85" t="n">
         <v>36</v>
@@ -16961,10 +16961,10 @@
         <v>120</v>
       </c>
       <c r="AN85" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO85" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP85" t="n">
         <v>15.5</v>
@@ -16988,7 +16988,7 @@
         <v>19.5</v>
       </c>
       <c r="AW85" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="AX85" t="n">
         <v>9</v>
@@ -17009,7 +17009,7 @@
         <v>15</v>
       </c>
       <c r="BD85" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BE85" t="n">
         <v>40</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="G86" t="n">
         <v>1.97</v>
@@ -17062,13 +17062,13 @@
         <v>5.4</v>
       </c>
       <c r="I86" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J86" t="n">
         <v>3.25</v>
       </c>
       <c r="K86" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G87" t="n">
         <v>2.04</v>
@@ -17277,7 +17277,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q87" t="n">
         <v>1.93</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -17504,7 +17504,7 @@
         <v>14</v>
       </c>
       <c r="AA88" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AB88" t="n">
         <v>14</v>
@@ -17516,7 +17516,7 @@
         <v>11</v>
       </c>
       <c r="AE88" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AF88" t="n">
         <v>32</v>
@@ -17546,7 +17546,7 @@
         <v>60</v>
       </c>
       <c r="AO88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP88" t="n">
         <v>12</v>
@@ -17558,7 +17558,7 @@
         <v>12</v>
       </c>
       <c r="AS88" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT88" t="n">
         <v>12</v>
@@ -17582,7 +17582,7 @@
         <v>16</v>
       </c>
       <c r="BA88" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB88" t="n">
         <v>60</v>
@@ -17594,7 +17594,7 @@
         <v>48</v>
       </c>
       <c r="BE88" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF88" t="n">
         <v>42</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -17638,16 +17638,16 @@
         <v>3.5</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H89" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I89" t="n">
         <v>2.3</v>
       </c>
       <c r="J89" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K89" t="n">
         <v>3.75</v>
@@ -17668,7 +17668,7 @@
         <v>1.87</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G92" t="n">
         <v>1.41</v>
@@ -18232,7 +18232,7 @@
         <v>5.9</v>
       </c>
       <c r="K92" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18247,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -18414,13 +18414,13 @@
         <v>1.67</v>
       </c>
       <c r="G93" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="H93" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I93" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J93" t="n">
         <v>3.4</v>
@@ -18435,13 +18435,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O93" t="n">
         <v>1.43</v>
       </c>
       <c r="P93" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q93" t="n">
         <v>2.26</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G94" t="n">
         <v>1.85</v>
@@ -18617,7 +18617,7 @@
         <v>5.4</v>
       </c>
       <c r="J94" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K94" t="n">
         <v>4.3</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19384,7 @@
         <v>2.64</v>
       </c>
       <c r="G98" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H98" t="n">
         <v>2.56</v>
@@ -19396,7 +19396,7 @@
         <v>3.5</v>
       </c>
       <c r="K98" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19605,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="Q99" t="n">
         <v>2.4</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q101" t="n">
         <v>2.92</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
         <v>3.7</v>
       </c>
       <c r="I102" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J102" t="n">
         <v>3.8</v>
@@ -20187,7 +20187,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q102" t="n">
         <v>1.71</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -20548,13 +20548,13 @@
         <v>2.1</v>
       </c>
       <c r="G104" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H104" t="n">
         <v>3.45</v>
       </c>
       <c r="I104" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J104" t="n">
         <v>3.85</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20793,7 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y105" t="n">
         <v>44</v>
@@ -20805,22 +20805,22 @@
         <v>1000</v>
       </c>
       <c r="AB105" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC105" t="n">
         <v>15.5</v>
       </c>
       <c r="AD105" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AE105" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AF105" t="n">
         <v>7.2</v>
       </c>
       <c r="AG105" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH105" t="n">
         <v>46</v>
@@ -20832,13 +20832,13 @@
         <v>9</v>
       </c>
       <c r="AK105" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL105" t="n">
         <v>50</v>
       </c>
       <c r="AM105" t="n">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AN105" t="n">
         <v>4.6</v>
@@ -20868,7 +20868,7 @@
         <v>28</v>
       </c>
       <c r="AW105" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AX105" t="n">
         <v>6.6</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -20936,10 +20936,10 @@
         <v>2.9</v>
       </c>
       <c r="G106" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H106" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I106" t="n">
         <v>2.76</v>
@@ -20948,7 +20948,7 @@
         <v>3.4</v>
       </c>
       <c r="K106" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
         <v>1.72</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -21127,19 +21127,19 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G107" t="n">
         <v>3.15</v>
       </c>
       <c r="H107" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I107" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J107" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K107" t="n">
         <v>4</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21405,7 +21405,7 @@
         <v>21</v>
       </c>
       <c r="AH108" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI108" t="n">
         <v>25</v>
@@ -21465,7 +21465,7 @@
         <v>21</v>
       </c>
       <c r="BB108" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC108" t="n">
         <v>42</v>
@@ -21474,7 +21474,7 @@
         <v>40</v>
       </c>
       <c r="BE108" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BF108" t="n">
         <v>34</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -21515,22 +21515,22 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H109" t="n">
         <v>4</v>
       </c>
       <c r="I109" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J109" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K109" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -21903,16 +21903,16 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G111" t="n">
         <v>3.3</v>
       </c>
       <c r="H111" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I111" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J111" t="n">
         <v>3.6</v>
@@ -21936,16 +21936,16 @@
         <v>2.08</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R111" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S111" t="n">
         <v>3.15</v>
       </c>
       <c r="T111" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U111" t="n">
         <v>2.3</v>
@@ -22005,7 +22005,7 @@
         <v>80</v>
       </c>
       <c r="AN111" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO111" t="n">
         <v>17.5</v>
@@ -22047,13 +22047,13 @@
         <v>29</v>
       </c>
       <c r="BB111" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC111" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BD111" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE111" t="n">
         <v>10</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -22103,10 +22103,10 @@
         <v>1.82</v>
       </c>
       <c r="H112" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I112" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J112" t="n">
         <v>4</v>
@@ -22127,7 +22127,7 @@
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q112" t="n">
         <v>1.72</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -22321,10 +22321,10 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -22488,19 +22488,19 @@
         <v>4.2</v>
       </c>
       <c r="G114" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H114" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="I114" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="J114" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K114" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -22679,16 +22679,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G115" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H115" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I115" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J115" t="n">
         <v>4.1</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -23267,7 +23267,7 @@
         <v>4.5</v>
       </c>
       <c r="H118" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="I118" t="n">
         <v>2.68</v>
@@ -23276,7 +23276,7 @@
         <v>2.46</v>
       </c>
       <c r="K118" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -23294,7 +23294,7 @@
         <v>1.69</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>
@@ -23485,10 +23485,10 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-05 00:32:27</t>
+          <t>2026-03-05 02:49:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-07.xlsx
@@ -763,16 +763,16 @@
         <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -796,16 +796,16 @@
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U2" t="n">
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W2" t="n">
         <v>1.55</v>
@@ -817,7 +817,7 @@
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>46</v>
@@ -859,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
         <v>27</v>
@@ -874,7 +874,7 @@
         <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -898,10 +898,10 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -910,7 +910,7 @@
         <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
         <v>2.26</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
         <v>1.02</v>
@@ -984,34 +984,34 @@
         <v>3.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="T3" t="n">
         <v>1.39</v>
       </c>
       <c r="U3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V3" t="n">
         <v>1.47</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X3" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA3" t="n">
         <v>55</v>
@@ -1020,101 +1020,101 @@
         <v>24</v>
       </c>
       <c r="AC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG3" t="n">
         <v>13</v>
       </c>
-      <c r="AD3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AJ3" t="n">
         <v>34</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN3" t="n">
         <v>7.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>42</v>
       </c>
       <c r="AT3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AU3" t="n">
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>20</v>
       </c>
-      <c r="BB3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>19</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
         <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="n">
         <v>4.8</v>
@@ -1163,152 +1163,152 @@
         <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1351,16 +1351,16 @@
         <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
         <v>4.6</v>
@@ -1375,134 +1375,134 @@
         <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1539,19 +1539,19 @@
         <v>2.56</v>
       </c>
       <c r="H6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I6" t="n">
         <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M6" t="n">
         <v>1.04</v>
@@ -1560,10 +1560,10 @@
         <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
         <v>1.6</v>
@@ -1572,16 +1572,16 @@
         <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U6" t="n">
         <v>2.66</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
         <v>1.64</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="H7" t="n">
         <v>2.98</v>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="K7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>710</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
         <v>4.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>2.82</v>
       </c>
       <c r="G11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J11" t="n">
         <v>3.45</v>
       </c>
-      <c r="H11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G12" t="n">
         <v>1.84</v>
@@ -2706,7 +2706,7 @@
         <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.82</v>
+        <v>1.02</v>
       </c>
       <c r="O12" t="n">
         <v>1.13</v>
       </c>
       <c r="P12" t="n">
-        <v>2.82</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.78</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.9</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>2.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H15" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I15" t="n">
         <v>3.05</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>2.16</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
         <v>4.1</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
         <v>1.75</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H18" t="n">
         <v>1.65</v>
@@ -3876,7 +3876,7 @@
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="I19" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="J19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K19" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>2.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H20" t="n">
         <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>1.09</v>
       </c>
       <c r="H21" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J21" t="n">
         <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1.82</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>5.7</v>
@@ -4652,37 +4652,37 @@
         <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V22" t="n">
         <v>1.21</v>
@@ -4691,7 +4691,7 @@
         <v>2.2</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y22" t="n">
         <v>15.5</v>
@@ -4700,10 +4700,10 @@
         <v>44</v>
       </c>
       <c r="AA22" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
@@ -4712,7 +4712,7 @@
         <v>23</v>
       </c>
       <c r="AE22" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
         <v>9.6</v>
@@ -4724,28 +4724,28 @@
         <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
         <v>19</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
         <v>13</v>
@@ -4757,7 +4757,7 @@
         <v>44</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU22" t="n">
         <v>7.4</v>
@@ -4766,41 +4766,41 @@
         <v>19.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB22" t="n">
         <v>16.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="H23" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="I23" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="G24" t="n">
         <v>4.2</v>
       </c>
       <c r="H24" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I24" t="n">
         <v>2.16</v>
@@ -5040,7 +5040,7 @@
         <v>3.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="G25" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="H25" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>3.7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>3.3</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="G28" t="n">
         <v>5.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="I28" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
         <v>1.97</v>
@@ -6010,7 +6010,7 @@
         <v>3.7</v>
       </c>
       <c r="K29" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="G30" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="I30" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>2.08</v>
       </c>
       <c r="G31" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K31" t="n">
         <v>4.3</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         <v>1.01</v>
       </c>
       <c r="K32" t="n">
-        <v>410</v>
+        <v>950</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
         <v>1.24</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
         <v>1.01</v>
       </c>
       <c r="K41" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8520,10 +8520,10 @@
         <v>2.42</v>
       </c>
       <c r="G42" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H42" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I42" t="n">
         <v>3.5</v>
@@ -8532,7 +8532,7 @@
         <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q42" t="n">
         <v>1.94</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8711,22 +8711,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.27</v>
+        <v>1.04</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="H43" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
         <v>1000</v>
       </c>
       <c r="J43" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="K43" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8738,13 +8738,13 @@
         <v>1.03</v>
       </c>
       <c r="O43" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P43" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="G44" t="n">
         <v>2.16</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="I44" t="n">
         <v>4.7</v>
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q44" t="n">
         <v>1.71</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9389,7 @@
         <v>100</v>
       </c>
       <c r="AL46" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AM46" t="n">
         <v>190</v>
@@ -9404,7 +9404,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR46" t="n">
         <v>8.4</v>
@@ -9443,7 +9443,7 @@
         <v>36</v>
       </c>
       <c r="BD46" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE46" t="n">
         <v>46</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
         <v>1.01</v>
       </c>
       <c r="K47" t="n">
-        <v>650</v>
+        <v>950</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -9908,13 +9908,13 @@
         <v>2.46</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R49" t="n">
         <v>1.6</v>
       </c>
       <c r="S49" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T49" t="n">
         <v>1.58</v>
@@ -9956,7 +9956,7 @@
         <v>29</v>
       </c>
       <c r="AG49" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH49" t="n">
         <v>15</v>
@@ -9977,7 +9977,7 @@
         <v>65</v>
       </c>
       <c r="AN49" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO49" t="n">
         <v>12</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
         <v>4</v>
       </c>
       <c r="O50" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P50" t="n">
         <v>2</v>
@@ -10129,7 +10129,7 @@
         <v>11.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA50" t="n">
         <v>36</v>
@@ -10189,7 +10189,7 @@
         <v>22</v>
       </c>
       <c r="AT50" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU50" t="n">
         <v>7.2</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G51" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
         <v>3.05</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3.1</v>
       </c>
       <c r="J51" t="n">
         <v>3.7</v>
@@ -10296,7 +10296,7 @@
         <v>2.24</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R51" t="n">
         <v>1.49</v>
@@ -10305,7 +10305,7 @@
         <v>2.86</v>
       </c>
       <c r="T51" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U51" t="n">
         <v>2.5</v>
@@ -10347,7 +10347,7 @@
         <v>12</v>
       </c>
       <c r="AH51" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI51" t="n">
         <v>40</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10487,13 +10487,13 @@
         <v>1.16</v>
       </c>
       <c r="P52" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R52" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S52" t="n">
         <v>2.2</v>
@@ -10541,7 +10541,7 @@
         <v>10.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI52" t="n">
         <v>75</v>
@@ -10562,13 +10562,13 @@
         <v>4.8</v>
       </c>
       <c r="AO52" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
         <v>27</v>
       </c>
       <c r="AQ52" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR52" t="n">
         <v>50</v>
@@ -10583,7 +10583,7 @@
         <v>11.5</v>
       </c>
       <c r="AV52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW52" t="n">
         <v>36</v>
@@ -10601,10 +10601,10 @@
         <v>48</v>
       </c>
       <c r="BB52" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC52" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>13</v>
       </c>
       <c r="BD52" t="n">
         <v>23</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
         <v>1.17</v>
       </c>
       <c r="P53" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q53" t="n">
         <v>1.54</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>6.4</v>
       </c>
       <c r="J54" t="n">
-        <v>2.48</v>
+        <v>2.92</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.4</v>
+        <v>2.54</v>
       </c>
       <c r="G55" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H55" t="n">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="J55" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -11069,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="Q55" t="n">
         <v>2.08</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="G57" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="H57" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="I57" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J57" t="n">
-        <v>2.48</v>
+        <v>3.3</v>
       </c>
       <c r="K57" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
         <v>1.01</v>
       </c>
       <c r="K58" t="n">
-        <v>510</v>
+        <v>950</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -11818,19 +11818,19 @@
         <v>4</v>
       </c>
       <c r="G59" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H59" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="I59" t="n">
         <v>2.12</v>
       </c>
       <c r="J59" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K59" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
         <v>2.52</v>
       </c>
       <c r="G60" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H60" t="n">
         <v>3.3</v>
@@ -12042,7 +12042,7 @@
         <v>1.64</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12227,7 +12227,7 @@
         <v>1.07</v>
       </c>
       <c r="N61" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O61" t="n">
         <v>1.32</v>
@@ -12236,7 +12236,7 @@
         <v>1.96</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R61" t="n">
         <v>1.37</v>
@@ -12257,10 +12257,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y61" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z61" t="n">
         <v>17.5</v>
@@ -12269,7 +12269,7 @@
         <v>40</v>
       </c>
       <c r="AB61" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC61" t="n">
         <v>7.6</v>
@@ -12278,7 +12278,7 @@
         <v>12.5</v>
       </c>
       <c r="AE61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF61" t="n">
         <v>21</v>
@@ -12299,7 +12299,7 @@
         <v>34</v>
       </c>
       <c r="AL61" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM61" t="n">
         <v>90</v>
@@ -12314,16 +12314,16 @@
         <v>13</v>
       </c>
       <c r="AQ61" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR61" t="n">
         <v>14.5</v>
       </c>
       <c r="AS61" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AT61" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU61" t="n">
         <v>7.2</v>
@@ -12332,7 +12332,7 @@
         <v>11</v>
       </c>
       <c r="AW61" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX61" t="n">
         <v>17</v>
@@ -12344,29 +12344,29 @@
         <v>15</v>
       </c>
       <c r="BA61" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB61" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="BC61" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BD61" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE61" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF61" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="BG61" t="n">
         <v>19.5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12397,16 +12397,16 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G62" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H62" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="I62" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>2.84</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
         <v>2.48</v>
       </c>
       <c r="J63" t="n">
-        <v>2.66</v>
+        <v>3.35</v>
       </c>
       <c r="K63" t="n">
         <v>7.2</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
         <v>2.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G65" t="n">
         <v>3.5</v>
@@ -13009,7 +13009,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q65" t="n">
         <v>1.86</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13176,13 +13176,13 @@
         <v>1.73</v>
       </c>
       <c r="G66" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H66" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I66" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>3.7</v>
@@ -13206,7 +13206,7 @@
         <v>1.84</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="G67" t="n">
         <v>2.58</v>
@@ -13376,7 +13376,7 @@
         <v>3.15</v>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J67" t="n">
         <v>3.15</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13564,16 +13564,16 @@
         <v>1.31</v>
       </c>
       <c r="G68" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="H68" t="n">
         <v>6</v>
       </c>
       <c r="I68" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="J68" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="K68" t="n">
         <v>7.2</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13761,7 +13761,7 @@
         <v>2.36</v>
       </c>
       <c r="H69" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I69" t="n">
         <v>3.85</v>
@@ -13779,10 +13779,10 @@
         <v>1.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O69" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P69" t="n">
         <v>1.64</v>
@@ -13800,7 +13800,7 @@
         <v>2.04</v>
       </c>
       <c r="U69" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V69" t="n">
         <v>0</v>
@@ -13857,13 +13857,13 @@
         <v>190</v>
       </c>
       <c r="AN69" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO69" t="n">
         <v>90</v>
       </c>
       <c r="AP69" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ69" t="n">
         <v>9.6</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -13961,7 +13961,7 @@
         <v>2.34</v>
       </c>
       <c r="J70" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="K70" t="n">
         <v>7.2</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
         <v>2.06</v>
       </c>
       <c r="G72" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H72" t="n">
         <v>3.95</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14531,10 +14531,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="G73" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H73" t="n">
         <v>1.91</v>
@@ -14546,7 +14546,7 @@
         <v>3.3</v>
       </c>
       <c r="K73" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -14561,7 +14561,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q73" t="n">
         <v>1.58</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G77" t="n">
         <v>1.84</v>
@@ -15316,13 +15316,13 @@
         <v>4.6</v>
       </c>
       <c r="I77" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J77" t="n">
         <v>4.1</v>
       </c>
       <c r="K77" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15695,7 +15695,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G79" t="n">
         <v>1.38</v>
@@ -15707,7 +15707,7 @@
         <v>13.5</v>
       </c>
       <c r="J79" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K79" t="n">
         <v>6.6</v>
@@ -15725,7 +15725,7 @@
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="Q79" t="n">
         <v>1.47</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
         <v>1.01</v>
       </c>
       <c r="K80" t="n">
-        <v>630</v>
+        <v>950</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G81" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H81" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I81" t="n">
         <v>1.74</v>
@@ -16098,7 +16098,7 @@
         <v>3.7</v>
       </c>
       <c r="K81" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q81" t="n">
         <v>1.66</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16277,13 +16277,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="G82" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H82" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I82" t="n">
         <v>6.6</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16340,7 +16340,7 @@
         <v>55</v>
       </c>
       <c r="AA82" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB82" t="n">
         <v>8.199999999999999</v>
@@ -16352,7 +16352,7 @@
         <v>25</v>
       </c>
       <c r="AE82" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF82" t="n">
         <v>9.6</v>
@@ -16367,7 +16367,7 @@
         <v>95</v>
       </c>
       <c r="AJ82" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AK82" t="n">
         <v>18.5</v>
@@ -16379,7 +16379,7 @@
         <v>150</v>
       </c>
       <c r="AN82" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO82" t="n">
         <v>140</v>
@@ -16394,7 +16394,7 @@
         <v>42</v>
       </c>
       <c r="AS82" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT82" t="n">
         <v>7.4</v>
@@ -16418,10 +16418,10 @@
         <v>18.5</v>
       </c>
       <c r="BA82" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB82" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC82" t="n">
         <v>16</v>
@@ -16430,17 +16430,17 @@
         <v>30</v>
       </c>
       <c r="BE82" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF82" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG82" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G84" t="n">
         <v>4.7</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -16859,7 +16859,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G85" t="n">
         <v>1.65</v>
@@ -16889,7 +16889,7 @@
         <v>1.29</v>
       </c>
       <c r="P85" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q85" t="n">
         <v>1.84</v>
@@ -16949,7 +16949,7 @@
         <v>1000</v>
       </c>
       <c r="AJ85" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK85" t="n">
         <v>17</v>
@@ -17000,7 +17000,7 @@
         <v>19</v>
       </c>
       <c r="BA85" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB85" t="n">
         <v>14</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="G86" t="n">
         <v>1.97</v>
@@ -17068,7 +17068,7 @@
         <v>3.25</v>
       </c>
       <c r="K86" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G87" t="n">
         <v>2.04</v>
@@ -17277,7 +17277,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q87" t="n">
         <v>1.93</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -17441,10 +17441,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G88" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H88" t="n">
         <v>2.18</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -17641,10 +17641,10 @@
         <v>3.95</v>
       </c>
       <c r="H89" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I89" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J89" t="n">
         <v>3.45</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -17838,10 +17838,10 @@
         <v>2.04</v>
       </c>
       <c r="I90" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J90" t="n">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="K90" t="n">
         <v>1000</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -18035,7 +18035,7 @@
         <v>3.7</v>
       </c>
       <c r="J91" t="n">
-        <v>2.52</v>
+        <v>3.05</v>
       </c>
       <c r="K91" t="n">
         <v>6.2</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -18229,10 +18229,10 @@
         <v>9.4</v>
       </c>
       <c r="J92" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -18250,7 +18250,7 @@
         <v>3.45</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -18414,19 +18414,19 @@
         <v>1.67</v>
       </c>
       <c r="G93" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H93" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J93" t="n">
         <v>3.4</v>
       </c>
       <c r="K93" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -18435,7 +18435,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O93" t="n">
         <v>1.43</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -18605,7 +18605,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G94" t="n">
         <v>1.85</v>
@@ -18617,7 +18617,7 @@
         <v>5.4</v>
       </c>
       <c r="J94" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K94" t="n">
         <v>4.3</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
         <v>2.52</v>
       </c>
       <c r="J95" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="K95" t="n">
         <v>6.2</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
         <v>1000</v>
       </c>
       <c r="J96" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="K96" t="n">
         <v>1000</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
         <v>2.66</v>
       </c>
       <c r="J97" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="K97" t="n">
         <v>7.2</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19396,7 +19396,7 @@
         <v>3.5</v>
       </c>
       <c r="K98" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19575,22 +19575,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="G99" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="I99" t="n">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="J99" t="n">
-        <v>2.62</v>
+        <v>2.96</v>
       </c>
       <c r="K99" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19605,7 +19605,7 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Q99" t="n">
         <v>2.4</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19781,10 +19781,10 @@
         <v>4.4</v>
       </c>
       <c r="J100" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="K100" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -19963,19 +19963,19 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="G101" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="H101" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="J101" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="K101" t="n">
         <v>3</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -20187,7 +20187,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q102" t="n">
         <v>1.71</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -20548,13 +20548,13 @@
         <v>2.1</v>
       </c>
       <c r="G104" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H104" t="n">
         <v>3.45</v>
       </c>
       <c r="I104" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J104" t="n">
         <v>3.85</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
         <v>1.25</v>
       </c>
       <c r="G105" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
@@ -20751,7 +20751,7 @@
         <v>16</v>
       </c>
       <c r="J105" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K105" t="n">
         <v>7.2</v>
@@ -20805,16 +20805,16 @@
         <v>1000</v>
       </c>
       <c r="AB105" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC105" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD105" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE105" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AF105" t="n">
         <v>7.2</v>
@@ -20823,7 +20823,7 @@
         <v>11.5</v>
       </c>
       <c r="AH105" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI105" t="n">
         <v>1000</v>
@@ -20832,13 +20832,13 @@
         <v>9</v>
       </c>
       <c r="AK105" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL105" t="n">
         <v>50</v>
       </c>
       <c r="AM105" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN105" t="n">
         <v>4.6</v>
@@ -20847,7 +20847,7 @@
         <v>1000</v>
       </c>
       <c r="AP105" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AQ105" t="n">
         <v>36</v>
@@ -20856,7 +20856,7 @@
         <v>42</v>
       </c>
       <c r="AS105" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AT105" t="n">
         <v>7.8</v>
@@ -20868,7 +20868,7 @@
         <v>28</v>
       </c>
       <c r="AW105" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AX105" t="n">
         <v>6.6</v>
@@ -20877,7 +20877,7 @@
         <v>10</v>
       </c>
       <c r="AZ105" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BA105" t="n">
         <v>48</v>
@@ -20895,14 +20895,14 @@
         <v>50</v>
       </c>
       <c r="BF105" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG105" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -20933,22 +20933,22 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G106" t="n">
         <v>3.2</v>
       </c>
       <c r="H106" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="I106" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="J106" t="n">
         <v>3.4</v>
       </c>
       <c r="K106" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -20966,7 +20966,7 @@
         <v>1.72</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -21127,22 +21127,22 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G107" t="n">
         <v>3.15</v>
       </c>
       <c r="H107" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I107" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="J107" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K107" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -21157,10 +21157,10 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -21327,7 +21327,7 @@
         <v>5.3</v>
       </c>
       <c r="H108" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I108" t="n">
         <v>1.68</v>
@@ -21336,7 +21336,7 @@
         <v>4.7</v>
       </c>
       <c r="K108" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21366,7 +21366,7 @@
         <v>1.6</v>
       </c>
       <c r="U108" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="V108" t="n">
         <v>0</v>
@@ -21375,13 +21375,13 @@
         <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Y108" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z108" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA108" t="n">
         <v>19</v>
@@ -21393,22 +21393,22 @@
         <v>11.5</v>
       </c>
       <c r="AD108" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE108" t="n">
         <v>15</v>
       </c>
       <c r="AF108" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG108" t="n">
         <v>21</v>
       </c>
       <c r="AH108" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI108" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ108" t="n">
         <v>140</v>
@@ -21417,37 +21417,37 @@
         <v>60</v>
       </c>
       <c r="AL108" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM108" t="n">
         <v>60</v>
       </c>
       <c r="AN108" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AO108" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AP108" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ108" t="n">
         <v>12</v>
       </c>
       <c r="AR108" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS108" t="n">
         <v>16.5</v>
       </c>
       <c r="AT108" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU108" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AV108" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW108" t="n">
         <v>14</v>
@@ -21465,26 +21465,26 @@
         <v>21</v>
       </c>
       <c r="BB108" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC108" t="n">
         <v>42</v>
       </c>
       <c r="BD108" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE108" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="BF108" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG108" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -21545,10 +21545,10 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -21936,7 +21936,7 @@
         <v>2.08</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R111" t="n">
         <v>1.42</v>
@@ -21945,7 +21945,7 @@
         <v>3.15</v>
       </c>
       <c r="T111" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U111" t="n">
         <v>2.3</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
         <v>1.82</v>
       </c>
       <c r="H112" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I112" t="n">
         <v>5.1</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -22303,7 +22303,7 @@
         <v>2.46</v>
       </c>
       <c r="J113" t="n">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="K113" t="n">
         <v>4.9</v>
@@ -22321,10 +22321,10 @@
         <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -22488,19 +22488,19 @@
         <v>4.2</v>
       </c>
       <c r="G114" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H114" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="I114" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="J114" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K114" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -22679,16 +22679,16 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G115" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H115" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I115" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="J115" t="n">
         <v>4.1</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -22876,19 +22876,19 @@
         <v>1.47</v>
       </c>
       <c r="G116" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="H116" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="I116" t="n">
         <v>9</v>
       </c>
       <c r="J116" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K116" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
         <v>2.68</v>
       </c>
       <c r="J118" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="K118" t="n">
         <v>5.2</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G119" t="n">
         <v>1.87</v>
@@ -23464,10 +23464,10 @@
         <v>2.14</v>
       </c>
       <c r="I119" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J119" t="n">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="K119" t="n">
         <v>1000</v>
@@ -23488,7 +23488,7 @@
         <v>1.6</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="R119" t="n">
         <v>0</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-05 02:49:09</t>
+          <t>2026-03-05 05:05:01</t>
         </is>
       </c>
     </row>
